--- a/output/full_scan/batch_seq6_2026-08-27.xlsx
+++ b/output/full_scan/batch_seq6_2026-08-27.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O117"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1746,21 +1746,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6279</v>
+        <v>6225</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>619.9436244333374</v>
+        <v>627.2039179184864</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>127.5</v>
+        <v>66</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>59.04968579840885</v>
+        <v>78.97154865841232</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>16.78416993460167</v>
+        <v>51.71079623557296</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4899068183922407</v>
+        <v>0.7006511843128723</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.1527243131508964</v>
+        <v>2.909825532127702</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6224</v>
+        <v>6279</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>616.1445493945221</v>
+        <v>619.9436244333374</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>76.2</v>
+        <v>127.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>64.68702671963624</v>
+        <v>59.04968579840885</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.75335490554575</v>
+        <v>16.78416993460167</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.045227467565479</v>
+        <v>0.4899068183922407</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>2.324814524864979</v>
+        <v>-0.1527243131508964</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6449</v>
+        <v>6224</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>615.9430878188858</v>
+        <v>616.1445493945221</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>233</v>
+        <v>76.2</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>47.93277185148385</v>
+        <v>64.68702671963624</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>26.15572363579692</v>
+        <v>31.75335490554575</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.988626311644872</v>
+        <v>1.045227467565479</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>2.734776333346282</v>
+        <v>2.324814524864979</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>613.5727117507979</v>
+        <v>615.9430878188858</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1560</v>
+        <v>233</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>65.73329553173532</v>
+        <v>47.93277185148385</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>35.94501790994922</v>
+        <v>26.15572363579692</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.9906350441492636</v>
+        <v>1.988626311644872</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>14.48042025023459</v>
+        <v>2.734776333346282</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6175</v>
+        <v>6446</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>602.8561678490728</v>
+        <v>613.5727117507979</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>74.2</v>
+        <v>1560</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>41.26765258094702</v>
+        <v>65.73329553173532</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>20.55618893748282</v>
+        <v>35.94501790994922</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.188679943886496</v>
+        <v>0.9906350441492636</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.5730590885676747</v>
+        <v>14.48042025023459</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6419</v>
+        <v>6175</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>590.2994230566159</v>
+        <v>602.8561678490728</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>154</v>
+        <v>74.2</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>52.10969393383017</v>
+        <v>41.26765258094702</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>23.034675476047</v>
+        <v>20.55618893748282</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.2762133967014958</v>
+        <v>1.188679943886496</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.722939978493053</v>
+        <v>0.5730590885676747</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6207</v>
+        <v>6419</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>587.5606488634621</v>
+        <v>590.2994230566159</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>49.19478427276558</v>
+        <v>52.10969393383017</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>14.51022021466858</v>
+        <v>23.034675476047</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.953728735713992</v>
+        <v>0.2762133967014958</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1.395349649326484</v>
+        <v>-0.722939978493053</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6265</v>
+        <v>6207</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>583.2488067734528</v>
+        <v>587.5606488634621</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>58.1</v>
+        <v>108</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>54.84000297065366</v>
+        <v>49.19478427276558</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23.29603475347119</v>
+        <v>14.51022021466858</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5262346521909952</v>
+        <v>1.953728735713992</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0307565883023435</v>
+        <v>1.395349649326484</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6227</v>
+        <v>6265</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>569.6272897740486</v>
+        <v>583.2488067734528</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>125</v>
+        <v>58.1</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>57.60418484480008</v>
+        <v>54.84000297065366</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>10.92577436502908</v>
+        <v>23.29603475347119</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3.757913390799154</v>
+        <v>0.5262346521909952</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.1946381079626531</v>
+        <v>0.0307565883023435</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6173</v>
+        <v>6227</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>567.0426198422796</v>
+        <v>569.6272897740486</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>217.5</v>
+        <v>125</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>55.09351969529265</v>
+        <v>57.60418484480008</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>18.14151412871825</v>
+        <v>10.92577436502908</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.8130526955699633</v>
+        <v>3.757913390799154</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>3.93273239842955</v>
+        <v>-0.1946381079626531</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6220</v>
+        <v>6173</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>563.372972791782</v>
+        <v>567.0426198422796</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>26.05</v>
+        <v>217.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>43.41569951833669</v>
+        <v>55.09351969529265</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>23.95220842503576</v>
+        <v>18.14151412871825</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.997626275286056</v>
+        <v>0.8130526955699633</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.3035432889210363</v>
+        <v>3.93273239842955</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6204</v>
+        <v>6220</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>562.1088849843521</v>
+        <v>563.372972791782</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>89</v>
+        <v>26.05</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>57.90420055172869</v>
+        <v>43.41569951833669</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>17.63181575900663</v>
+        <v>23.95220842503576</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.583222198151214</v>
+        <v>1.997626275286056</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1.410268942793219</v>
+        <v>0.3035432889210363</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6271</v>
+        <v>6204</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>559.6405768775849</v>
+        <v>562.1088849843521</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>57.77445494340788</v>
+        <v>57.90420055172869</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.73868661136515</v>
+        <v>17.63181575900663</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.085053326754367</v>
+        <v>1.583222198151214</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>3.407047478600147</v>
+        <v>1.410268942793219</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6477</v>
+        <v>6271</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>554.333379586995</v>
+        <v>559.6405768775849</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>38.15</v>
+        <v>210</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>55.61136155802543</v>
+        <v>57.77445494340788</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18.48550009284065</v>
+        <v>13.73868661136515</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.742901877643565</v>
+        <v>1.085053326754367</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1026481675589435</v>
+        <v>3.407047478600147</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6218</v>
+        <v>6477</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>550.8880938607831</v>
+        <v>554.333379586995</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>39.95</v>
+        <v>38.15</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>64.20730582233293</v>
+        <v>55.61136155802543</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>29.32105875101879</v>
+        <v>18.48550009284065</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.412731249670584</v>
+        <v>1.742901877643565</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.4797221306493732</v>
+        <v>0.1026481675589435</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6209</v>
+        <v>6218</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>546.8906658946066</v>
+        <v>550.8880938607831</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>76.5</v>
+        <v>39.95</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>57.74780399107588</v>
+        <v>64.20730582233293</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>12.58498418542916</v>
+        <v>29.32105875101879</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4.218720032561902</v>
+        <v>1.412731249670584</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.7949788326792024</v>
+        <v>0.4797221306493732</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6292</v>
+        <v>6209</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>532.4064531380038</v>
+        <v>546.8906658946066</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>61.4</v>
+        <v>76.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>54.29346851321301</v>
+        <v>57.74780399107588</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>25.44755726582328</v>
+        <v>12.58498418542916</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.2492627180621283</v>
+        <v>4.218720032561902</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.1799907604365214</v>
+        <v>0.7949788326792024</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6277</v>
+        <v>6292</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>529.9491391413443</v>
+        <v>532.4064531380038</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.52475387071584</v>
+        <v>54.29346851321301</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>38.11826004969415</v>
+        <v>25.44755726582328</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3610831226172822</v>
+        <v>0.2492627180621283</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.4344851379595196</v>
+        <v>-0.1799907604365214</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6472</v>
+        <v>6277</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>529.6290875051349</v>
+        <v>529.9491391413443</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>439.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>54.86766630403056</v>
+        <v>51.52475387071584</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>30.38230269846272</v>
+        <v>38.11826004969415</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.250456044578128</v>
+        <v>0.3610831226172822</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>3.782835635504359</v>
+        <v>-0.4344851379595196</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6167</v>
+        <v>6472</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>524.3082357857987</v>
+        <v>529.6290875051349</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>10.95</v>
+        <v>439.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>56.33917265092089</v>
+        <v>54.86766630403056</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>13.58031164978954</v>
+        <v>30.38230269846272</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2.066901738352045</v>
+        <v>1.250456044578128</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.08369293551074269</v>
+        <v>3.782835635504359</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6206</v>
+        <v>6167</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>512.7462204348402</v>
+        <v>524.3082357857987</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>140.5</v>
+        <v>10.95</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>51.19044376557444</v>
+        <v>56.33917265092089</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>25.2017912412354</v>
+        <v>13.58031164978954</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.210503597914283</v>
+        <v>2.066901738352045</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.047102464895671</v>
+        <v>0.08369293551074269</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6411</v>
+        <v>6206</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>511.520797953779</v>
+        <v>512.7462204348402</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>79.5</v>
+        <v>140.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.4789791021649</v>
+        <v>51.19044376557444</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>15.73423693336333</v>
+        <v>25.2017912412354</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.7061657539267587</v>
+        <v>0.210503597914283</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.7755235421660407</v>
+        <v>-1.047102464895671</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6405</v>
+        <v>6411</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>503.9915540852726</v>
+        <v>511.520797953779</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>40.3</v>
+        <v>79.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46.86821500703356</v>
+        <v>48.4789791021649</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>25.56562698625925</v>
+        <v>15.73423693336333</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.720820688350131</v>
+        <v>0.7061657539267587</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.8469139491572855</v>
+        <v>0.7755235421660407</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6464</v>
+        <v>6405</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>503.8439881848532</v>
+        <v>503.9915540852726</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>77.90000000000001</v>
+        <v>40.3</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>46.46371559568259</v>
+        <v>46.86821500703356</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>29.42616229105386</v>
+        <v>25.56562698625925</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.1761905985981869</v>
+        <v>2.720820688350131</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0332550224547008</v>
+        <v>0.8469139491572855</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6245</v>
+        <v>6464</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>502.7549792503377</v>
+        <v>503.8439881848532</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>83.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>52.94250361124868</v>
+        <v>46.46371559568259</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>11.804463595152</v>
+        <v>29.42616229105386</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6211457646041798</v>
+        <v>0.1761905985981869</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.1783725182669137</v>
+        <v>0.0332550224547008</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6236</v>
+        <v>6245</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>495.182736319378</v>
+        <v>502.7549792503377</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>17.45</v>
+        <v>83.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>58.56596814255006</v>
+        <v>52.94250361124868</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10.62038184111301</v>
+        <v>11.804463595152</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.958085597759324</v>
+        <v>0.6211457646041798</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.057162494045102</v>
+        <v>-0.1783725182669137</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6174</v>
+        <v>6236</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>492.1005043823594</v>
+        <v>495.182736319378</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>45</v>
+        <v>17.45</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.88767601462276</v>
+        <v>58.56596814255006</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>13.8071958810746</v>
+        <v>10.62038184111301</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4415430825736443</v>
+        <v>2.958085597759324</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.5102549492006965</v>
+        <v>1.057162494045102</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6409</v>
+        <v>6174</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>483.1542752639603</v>
+        <v>492.1005043823594</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1045</v>
+        <v>45</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>55.23274969979514</v>
+        <v>49.88767601462276</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>19.65360594889947</v>
+        <v>13.8071958810746</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9328637152552608</v>
+        <v>0.4415430825736443</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>3.506091267517757</v>
+        <v>0.5102549492006965</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6237</v>
+        <v>6409</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>479.5766006633116</v>
+        <v>483.1542752639603</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>34.8</v>
+        <v>1045</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>48.66729025095434</v>
+        <v>55.23274969979514</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>24.08243162372197</v>
+        <v>19.65360594889947</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.052384629266402</v>
+        <v>0.9328637152552608</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.4098674116422378</v>
+        <v>3.506091267517757</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6285</v>
+        <v>6237</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>477.8633711599276</v>
+        <v>479.5766006633116</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>245</v>
+        <v>34.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>51.42364073050402</v>
+        <v>48.66729025095434</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15.72068173049982</v>
+        <v>24.08243162372197</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.441675688707351</v>
+        <v>1.052384629266402</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.4444313776967163</v>
+        <v>0.4098674116422378</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6423</v>
+        <v>6285</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>466.7477478870817</v>
+        <v>477.8633711599276</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>81.5</v>
+        <v>245</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>58.3852732908355</v>
+        <v>51.42364073050402</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>15.77293628376656</v>
+        <v>15.72068173049982</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5016471369601443</v>
+        <v>1.441675688707351</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.4093047323129173</v>
+        <v>0.4444313776967163</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6234</v>
+        <v>6423</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>448.0434622324622</v>
+        <v>466.7477478870817</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>36.7</v>
+        <v>81.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50.60478449833932</v>
+        <v>58.3852732908355</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.3883096312268</v>
+        <v>15.77293628376656</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7875833728851465</v>
+        <v>0.5016471369601443</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.3854288373037744</v>
+        <v>0.4093047323129173</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6177</v>
+        <v>6234</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>441.2150731922997</v>
+        <v>448.0434622324622</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>47.9</v>
+        <v>36.7</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>51.54912985028621</v>
+        <v>50.60478449833932</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22.94132681441765</v>
+        <v>20.3883096312268</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4720709233914665</v>
+        <v>0.7875833728851465</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.06870463492030519</v>
+        <v>0.3854288373037744</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6261</v>
+        <v>6177</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>430.1184819491936</v>
+        <v>441.2150731922997</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.36580918176321</v>
+        <v>51.54912985028621</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>25.92182320182519</v>
+        <v>22.94132681441765</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.506080184892399</v>
+        <v>0.4720709233914665</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.9191747330913153</v>
+        <v>-0.06870463492030519</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6435</v>
+        <v>6261</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>422.2931534962585</v>
+        <v>430.1184819491936</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>263.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>48.9108993047255</v>
+        <v>46.36580918176321</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>16.67926137049172</v>
+        <v>25.92182320182519</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.9116730723680584</v>
+        <v>1.506080184892399</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>3.111617975931788</v>
+        <v>0.9191747330913153</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6274</v>
+        <v>6435</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>417.5657394699555</v>
+        <v>422.2931534962585</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>1445</v>
+        <v>263.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.56786889892033</v>
+        <v>48.9108993047255</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>12.83901427558343</v>
+        <v>16.67926137049172</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.670890294545647</v>
+        <v>0.9116730723680584</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-5.569464528645415</v>
+        <v>3.111617975931788</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6462</v>
+        <v>6274</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>416.2878771992283</v>
+        <v>417.5657394699555</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>100.5</v>
+        <v>1445</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.66217448186525</v>
+        <v>48.56786889892033</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>12.30910157210796</v>
+        <v>12.83901427558343</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.9279941371553924</v>
+        <v>1.670890294545647</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.6338987431576795</v>
+        <v>-5.569464528645415</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6241</v>
+        <v>6462</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>413.4456595402743</v>
+        <v>416.2878771992283</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>17.65</v>
+        <v>100.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>62.86274637725741</v>
+        <v>49.66217448186525</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>23.50731982285693</v>
+        <v>12.30910157210796</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5305995190106255</v>
+        <v>0.9279941371553924</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.1578683933074181</v>
+        <v>0.6338987431576795</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6182</v>
+        <v>6241</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>411.3810800793126</v>
+        <v>413.4456595402743</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>109</v>
+        <v>17.65</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>48.405613735839</v>
+        <v>62.86274637725741</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12.946332214277</v>
+        <v>23.50731982285693</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7614642569505581</v>
+        <v>0.5305995190106255</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.9068437701025488</v>
+        <v>0.1578683933074181</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6415</v>
+        <v>6182</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>409.4932896796428</v>
+        <v>411.3810800793126</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>470.5</v>
+        <v>109</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>52.89431911582091</v>
+        <v>48.405613735839</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>11.57550923686913</v>
+        <v>12.946332214277</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.504359538454384</v>
+        <v>0.7614642569505581</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>5.401502466671408</v>
+        <v>0.9068437701025488</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6257</v>
+        <v>6415</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>407.2974192789693</v>
+        <v>409.4932896796428</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>204</v>
+        <v>470.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>48.32270896471538</v>
+        <v>52.89431911582091</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13.63350909383357</v>
+        <v>11.57550923686913</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.048898270038403</v>
+        <v>1.504359538454384</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.8679822622059099</v>
+        <v>5.401502466671408</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6284</v>
+        <v>6257</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>399.2339417410342</v>
+        <v>407.2974192789693</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>77.8</v>
+        <v>204</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,49 +3944,49 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.34805502749926</v>
+        <v>48.32270896471538</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.93524215243008</v>
+        <v>13.63350909383357</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.6406584815951419</v>
+        <v>1.048898270038403</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.7878930366212047</v>
+        <v>0.8679822622059099</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6163</v>
+        <v>6284</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>396.7659261139754</v>
+        <v>399.2339417410342</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>43.5</v>
+        <v>77.8</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,49 +3997,49 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>52.52454476483901</v>
+        <v>47.34805502749926</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16.41708056395844</v>
+        <v>17.93524215243008</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5406219643915496</v>
+        <v>0.6406584815951419</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.2778153689803602</v>
+        <v>0.7878930366212047</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6197</v>
+        <v>6163</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>396.7584122339106</v>
+        <v>396.7659261139754</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>308</v>
+        <v>43.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.57481322686467</v>
+        <v>52.52454476483901</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16.93669458323245</v>
+        <v>16.41708056395844</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.8632581620304356</v>
+        <v>0.5406219643915496</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>1.371344228821135</v>
+        <v>0.2778153689803602</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6222</v>
+        <v>6197</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>391.2928265074708</v>
+        <v>396.7584122339106</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>20.05</v>
+        <v>308</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.33754291450627</v>
+        <v>51.57481322686467</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>9.542448887721989</v>
+        <v>16.93669458323245</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.558260869565217</v>
+        <v>0.8632581620304356</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3947351962220311</v>
+        <v>1.371344228821135</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6223</v>
+        <v>6222</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>382.7808960641328</v>
+        <v>391.2928265074708</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>5090</v>
+        <v>20.05</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>39.72950634196207</v>
+        <v>51.33754291450627</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16.46405393240086</v>
+        <v>9.542448887721989</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.707756815021831</v>
+        <v>1.558260869565217</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-83.91010771860903</v>
+        <v>0.3947351962220311</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6432</v>
+        <v>6223</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>380.0869665702022</v>
+        <v>382.7808960641328</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>63.8</v>
+        <v>5090</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>40.11821467171292</v>
+        <v>39.72950634196207</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13.80699288712254</v>
+        <v>16.46405393240086</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.3557522000982056</v>
+        <v>2.707756815021831</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.9598406854172126</v>
+        <v>-83.91010771860903</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6270</v>
+        <v>6432</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>374.9811075460765</v>
+        <v>380.0869665702022</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>29.85</v>
+        <v>63.8</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>46.7570620948402</v>
+        <v>40.11821467171292</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10.17317689956134</v>
+        <v>13.80699288712254</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5273306182755232</v>
+        <v>0.3557522000982056</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>3</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.115678866244644</v>
+        <v>-0.9598406854172126</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6412</v>
+        <v>6270</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>363.8788256535523</v>
+        <v>374.9811075460765</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>78.5</v>
+        <v>29.85</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.82111871226887</v>
+        <v>46.7570620948402</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>26.17836525442699</v>
+        <v>10.17317689956134</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.8802268033480223</v>
+        <v>0.5273306182755232</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.3808067578329461</v>
+        <v>0.115678866244644</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6210</v>
+        <v>6412</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>356.0873381660404</v>
+        <v>363.8788256535523</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>18.05</v>
+        <v>78.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.59323522322114</v>
+        <v>44.82111871226887</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>7.214157647123484</v>
+        <v>26.17836525442699</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5076540552056265</v>
+        <v>0.8802268033480223</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.133238592429993</v>
+        <v>0.3808067578329461</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6215</v>
+        <v>6210</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>354.6830957104912</v>
+        <v>356.0873381660404</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>98.2</v>
+        <v>18.05</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>47.49997437552162</v>
+        <v>51.59323522322114</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.6857421727666</v>
+        <v>7.214157647123484</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.776926693389151</v>
+        <v>0.5076540552056265</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0115312419453571</v>
+        <v>0.133238592429993</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6283</v>
+        <v>6215</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>354.575481055815</v>
+        <v>354.6830957104912</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>20.1</v>
+        <v>98.2</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>42.55727797931045</v>
+        <v>47.49997437552162</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>32.34792396577512</v>
+        <v>13.6857421727666</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7868733491177492</v>
+        <v>0.776926693389151</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.1029767385301622</v>
+        <v>-0.0115312419453571</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6451</v>
+        <v>6283</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>342.5621086837976</v>
+        <v>354.575481055815</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>452</v>
+        <v>20.1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>52.67442735688263</v>
+        <v>42.55727797931045</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>11.06855917197467</v>
+        <v>32.34792396577512</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2.354567906675494</v>
+        <v>0.7868733491177492</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>5.769307952778412</v>
+        <v>0.1029767385301622</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6243</v>
+        <v>6451</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>341.0875492540233</v>
+        <v>342.5621086837976</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>42.4</v>
+        <v>452</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45.64990551788802</v>
+        <v>52.67442735688263</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>21.3342048966339</v>
+        <v>11.06855917197467</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8411972101145833</v>
+        <v>2.354567906675494</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.6039907151181529</v>
+        <v>5.769307952778412</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6239</v>
+        <v>6243</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>338.5935762129211</v>
+        <v>341.0875492540233</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>277</v>
+        <v>42.4</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>50.44797765957119</v>
+        <v>45.64990551788802</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>13.06348012913197</v>
+        <v>21.3342048966339</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.828117005366576</v>
+        <v>0.8411972101145833</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>2.67398181142308</v>
+        <v>-0.6039907151181529</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6441</v>
+        <v>6239</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>337.6008368352781</v>
+        <v>338.5935762129211</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>21.5</v>
+        <v>277</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.89728003579422</v>
+        <v>50.44797765957119</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>21.41414918172828</v>
+        <v>13.06348012913197</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.2616427149097757</v>
+        <v>1.828117005366576</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.029514104023495</v>
+        <v>2.67398181142308</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6442</v>
+        <v>6441</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>336.6153555149216</v>
+        <v>337.6008368352781</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1595</v>
+        <v>21.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>56.14422540837855</v>
+        <v>48.89728003579422</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>19.48694395073623</v>
+        <v>21.41414918172828</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.035913548167035</v>
+        <v>0.2616427149097757</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>18.62131202042988</v>
+        <v>-0.029514104023495</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6185</v>
+        <v>6442</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>332.1493691332566</v>
+        <v>336.6153555149216</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>12.6</v>
+        <v>1595</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>27.85960369995605</v>
+        <v>56.14422540837855</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>24.03047589966277</v>
+        <v>19.48694395073623</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.614936913325661</v>
+        <v>1.035913548167035</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0756532890507932</v>
+        <v>18.62131202042988</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6202</v>
+        <v>6185</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>330.6935757623624</v>
+        <v>332.1493691332566</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>59.2</v>
+        <v>12.6</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>50.80058845836269</v>
+        <v>27.85960369995605</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>14.21170925650396</v>
+        <v>24.03047589966277</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.462088409530997</v>
+        <v>1.614936913325661</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0065635406933595</v>
+        <v>-0.0756532890507932</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6196</v>
+        <v>6202</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>327.0100445302024</v>
+        <v>330.6935757623624</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>497.5</v>
+        <v>59.2</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>47.9823830350018</v>
+        <v>50.80058845836269</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>11.11310049499699</v>
+        <v>14.21170925650396</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.7129006246195684</v>
+        <v>0.462088409530997</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.445461931741745</v>
+        <v>-0.0065635406933595</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6443</v>
+        <v>6196</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>306.5286339874146</v>
+        <v>327.0100445302024</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>26.7</v>
+        <v>497.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.12569207532155</v>
+        <v>47.9823830350018</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13.97820324574174</v>
+        <v>11.11310049499699</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.073197041426991</v>
+        <v>0.7129006246195684</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.2820054225425572</v>
+        <v>0.445461931741745</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6194</v>
+        <v>6443</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>306.2616040346652</v>
+        <v>306.5286339874146</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>29.7</v>
+        <v>26.7</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>43.64268065368359</v>
+        <v>46.12569207532155</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>24.41041040372549</v>
+        <v>13.97820324574174</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.1054718327369433</v>
+        <v>1.073197041426991</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0845102708061579</v>
+        <v>0.2820054225425572</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6233</v>
+        <v>6194</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>302.2200536865566</v>
+        <v>306.2616040346652</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>21.8</v>
+        <v>29.7</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.97364237328794</v>
+        <v>43.64268065368359</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.94022633579221</v>
+        <v>24.41041040372549</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.205275836698622</v>
+        <v>0.1054718327369433</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1679327422925859</v>
+        <v>0.0845102708061579</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6266</v>
+        <v>6233</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>299.9486676355761</v>
+        <v>302.2200536865566</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>25.15</v>
+        <v>21.8</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>52.95215356364288</v>
+        <v>50.97364237328794</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>11.13186873237317</v>
+        <v>15.94022633579221</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5632081787254587</v>
+        <v>1.205275836698622</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0716904234979009</v>
+        <v>0.1679327422925859</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5138,21 +5138,21 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6184</v>
+        <v>6266</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>298.595202077796</v>
+        <v>299.9486676355761</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>41.45</v>
+        <v>25.15</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>25.70490976134264</v>
+        <v>52.95215356364288</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.0271439913321</v>
+        <v>11.13186873237317</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.714082424674679</v>
+        <v>0.5632081787254587</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0109087182239371</v>
+        <v>0.0716904234979009</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6191</v>
+        <v>6184</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>295.5134663406052</v>
+        <v>298.595202077796</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>83.09999999999999</v>
+        <v>41.45</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>42.43589944184029</v>
+        <v>25.70490976134264</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>28.35698755825117</v>
+        <v>22.0271439913321</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6175619092646252</v>
+        <v>1.714082424674679</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.2312574428318838</v>
+        <v>0.0109087182239371</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6438</v>
+        <v>6191</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>294.9398229458806</v>
+        <v>295.5134663406052</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>148.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>54.0950537516324</v>
+        <v>42.43589944184029</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.61139483065855</v>
+        <v>28.35698755825117</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.391438176272748</v>
+        <v>0.6175619092646252</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.7093799741831008</v>
+        <v>0.2312574428318838</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6188</v>
+        <v>6438</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>289.4250125644558</v>
+        <v>294.9398229458806</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>69.5</v>
+        <v>148.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>46.46081531562713</v>
+        <v>54.0950537516324</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>19.31392010626888</v>
+        <v>14.61139483065855</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.24785832686515</v>
+        <v>1.391438176272748</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.1124620267970446</v>
+        <v>0.7093799741831008</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6465</v>
+        <v>6188</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>288.7581533450913</v>
+        <v>289.4250125644558</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>46.5</v>
+        <v>69.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>40.83122274378279</v>
+        <v>46.46081531562713</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>15.68924954906356</v>
+        <v>19.31392010626888</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5717348434761482</v>
+        <v>1.24785832686515</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.3097472066034967</v>
+        <v>0.1124620267970446</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6244</v>
+        <v>6465</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>284.6909788910033</v>
+        <v>288.7581533450913</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>24.25</v>
+        <v>46.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46.38699058333941</v>
+        <v>40.83122274378279</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.94462102383009</v>
+        <v>15.68924954906356</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.8705085415261173</v>
+        <v>0.5717348434761482</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0620406198686276</v>
+        <v>0.3097472066034967</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6229</v>
+        <v>6244</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>281.0060042406503</v>
+        <v>284.6909788910033</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>23.7</v>
+        <v>24.25</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>47.48562221587743</v>
+        <v>46.38699058333941</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.88403924106945</v>
+        <v>16.94462102383009</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4808698652998647</v>
+        <v>0.8705085415261173</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,51 +5499,51 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.07002096276364909</v>
+        <v>0.0620406198686276</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6288</v>
+        <v>6229</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>274.3107407686553</v>
+        <v>281.0060042406503</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>20.95</v>
+        <v>23.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G96" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>43.58025174415962</v>
+        <v>47.48562221587743</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v/>
+        <v>13.88403924106945</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6831032524092705</v>
+        <v>0.4808698652998647</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,51 +5552,51 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0313138023965832</v>
+        <v>0.07002096276364909</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6192</v>
+        <v>6288</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>271.8466635641981</v>
+        <v>274.3107407686553</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>116.5</v>
+        <v>20.95</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="G97" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.26657100814429</v>
+        <v>43.58025174415962</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>18.25888653556222</v>
+        <v/>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6516026687772569</v>
+        <v>0.6831032524092705</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1307261474343863</v>
+        <v>0.0313138023965832</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6166</v>
+        <v>6192</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>268.4629016056404</v>
+        <v>271.8466635641981</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>117</v>
+        <v>116.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.53505840017748</v>
+        <v>50.26657100814429</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.68752514661066</v>
+        <v>18.25888653556222</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.381200983077805</v>
+        <v>0.6516026687772569</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-1.551636894933722</v>
+        <v>0.1307261474343863</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6230</v>
+        <v>6166</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>258.138976899541</v>
+        <v>268.4629016056404</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.74197206575581</v>
+        <v>40.53505840017748</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>17.34195735733286</v>
+        <v>15.68752514661066</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.032044973379868</v>
+        <v>0.381200983077805</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.6400649102834626</v>
+        <v>-1.551636894933722</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6165</v>
+        <v>6230</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>257.7706098297474</v>
+        <v>258.138976899541</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>48.05</v>
+        <v>110</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>46.58796104624594</v>
+        <v>47.74197206575581</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>10.36457893632072</v>
+        <v>17.34195735733286</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.2855957190680591</v>
+        <v>1.032044973379868</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0792275003523573</v>
+        <v>0.6400649102834626</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6198</v>
+        <v>6165</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>257.1133611480075</v>
+        <v>257.7706098297474</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>19.65</v>
+        <v>48.05</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.66509908412941</v>
+        <v>46.58796104624594</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>5.957647626643677</v>
+        <v>10.36457893632072</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.0643979866376591</v>
+        <v>0.2855957190680591</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.2411182515691116</v>
+        <v>-0.0792275003523573</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6414</v>
+        <v>6198</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>254.160789194872</v>
+        <v>257.1133611480075</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>393.5</v>
+        <v>19.65</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>42.61736116223893</v>
+        <v>51.66509908412941</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.44892894712812</v>
+        <v>5.957647626643677</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3337297340452832</v>
+        <v>0.0643979866376591</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-6.19518429024724</v>
+        <v>0.2411182515691116</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6176</v>
+        <v>6414</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>251.0324060787623</v>
+        <v>254.160789194872</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>95.5</v>
+        <v>393.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>59.66101200826864</v>
+        <v>42.61736116223893</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>28.65304687025939</v>
+        <v>18.44892894712812</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5234988317811624</v>
+        <v>0.3337297340452832</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>1.844988151706069</v>
+        <v>-6.19518429024724</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6417</v>
+        <v>6176</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>248.0022481125078</v>
+        <v>251.0324060787623</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>106</v>
+        <v>95.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>36.25788612758365</v>
+        <v>59.66101200826864</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>24.44116475386731</v>
+        <v>28.65304687025939</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4984329999839432</v>
+        <v>0.5234988317811624</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1360725682071941</v>
+        <v>1.844988151706069</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6208</v>
+        <v>6417</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>231.7194974185409</v>
+        <v>248.0022481125078</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>106</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.75243338606559</v>
+        <v>36.25788612758365</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>8.855367031229179</v>
+        <v>24.44116475386731</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4538354739187082</v>
+        <v>0.4984329999839432</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.378649152576834</v>
+        <v>0.1360725682071941</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6246</v>
+        <v>6208</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>230.018922356671</v>
+        <v>231.7194974185409</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>12.55</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>45.65471028113036</v>
+        <v>48.75243338606559</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>20.53521366576993</v>
+        <v>8.855367031229179</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3358940919900492</v>
+        <v>0.4538354739187082</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1003093111524074</v>
+        <v>0.378649152576834</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6470</v>
+        <v>6246</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>221.0157219985048</v>
+        <v>230.018922356671</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>41.7</v>
+        <v>12.55</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>31.47790788198487</v>
+        <v>45.65471028113036</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>45.24200980157727</v>
+        <v>20.53521366576993</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.305747616997572</v>
+        <v>0.3358940919900492</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.1692791265242839</v>
+        <v>0.1003093111524074</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6235</v>
+        <v>6470</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>218.959865629963</v>
+        <v>221.0157219985048</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>39.2</v>
+        <v>41.7</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>52.33936299904266</v>
+        <v>31.47790788198487</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.43646807099798</v>
+        <v>45.24200980157727</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.130150567078948</v>
+        <v>1.305747616997572</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.1474686836683338</v>
+        <v>0.1692791265242839</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6201</v>
+        <v>6235</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>195.9384742754995</v>
+        <v>218.959865629963</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>44.7</v>
+        <v>39.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>33.20138942294408</v>
+        <v>52.33936299904266</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>25.68379339356792</v>
+        <v>12.43646807099798</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.250045206321652</v>
+        <v>1.130150567078948</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0279425343533828</v>
+        <v>0.1474686836683338</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6282</v>
+        <v>6201</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>189.2807279905312</v>
+        <v>195.9384742754995</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>45.15</v>
+        <v>44.7</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.2783597406161</v>
+        <v>33.20138942294408</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.18843204978721</v>
+        <v>25.68379339356792</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.585128500530534</v>
+        <v>0.250045206321652</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1102064400842133</v>
+        <v>0.0279425343533828</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6272</v>
+        <v>6282</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>175.2513363168909</v>
+        <v>189.2807279905312</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>24.1</v>
+        <v>45.15</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>43.90364422614604</v>
+        <v>43.2783597406161</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>43.09913342562735</v>
+        <v>17.18843204978721</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6664597938358339</v>
+        <v>0.585128500530534</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.2425426745511598</v>
+        <v>0.1102064400842133</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6276</v>
+        <v>6272</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>168.840492838696</v>
+        <v>175.2513363168909</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>20.2</v>
+        <v>24.1</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>49.48054220529075</v>
+        <v>43.90364422614604</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>23.49337318819044</v>
+        <v>43.09913342562735</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.041598882020045</v>
+        <v>0.6664597938358339</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.2336167454512698</v>
+        <v>0.2425426745511598</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6216</v>
+        <v>6276</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>156.1804782787842</v>
+        <v>168.840492838696</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>21</v>
+        <v>20.2</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>32.02107746071242</v>
+        <v>49.48054220529075</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13.68463805902691</v>
+        <v>23.49337318819044</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.877825846658154</v>
+        <v>1.041598882020045</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.09799361129565939</v>
+        <v>0.2336167454512698</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6281</v>
+        <v>6216</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>149.9587408920906</v>
+        <v>156.1804782787842</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>51.5</v>
+        <v>21</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>48.84047952142263</v>
+        <v>32.02107746071242</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.23228331515577</v>
+        <v>13.68463805902691</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.864041778058947</v>
+        <v>0.877825846658154</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0016088624366497</v>
+        <v>-0.09799361129565939</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6189</v>
+        <v>6281</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>136.3089491708135</v>
+        <v>149.9587408920906</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>48.15</v>
+        <v>51.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>46.97933698210426</v>
+        <v>48.84047952142263</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>9.072147998135508</v>
+        <v>14.23228331515577</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5019934988153797</v>
+        <v>0.864041778058947</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0920261622945848</v>
+        <v>0.0016088624366497</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6228</v>
+        <v>6189</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>123.6159576626453</v>
+        <v>136.3089491708135</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>17.3</v>
+        <v>48.15</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>51.33841295316483</v>
+        <v>46.97933698210426</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>6.627924109969396</v>
+        <v>9.072147998135508</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.6877689279501968</v>
+        <v>0.5019934988153797</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.6265559535630787</v>
+        <v>0.0920261622945848</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,52 +6622,105 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
+        <v>6228</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>全譜</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>123.6159576626453</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>51.33841295316483</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>6.627924109969396</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.6877689279501968</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.6265559535630787</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
         <v>6203</v>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>海韻電</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="n">
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
         <v>85.61342333645224</v>
       </c>
-      <c r="E117" s="2" t="n">
+      <c r="E118" s="2" t="n">
         <v>59.7</v>
       </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="n">
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
         <v>31.14627398321021</v>
       </c>
-      <c r="I117" s="2" t="n">
+      <c r="I118" s="2" t="n">
         <v>17.3864784231491</v>
       </c>
-      <c r="J117" s="2" t="n">
+      <c r="J118" s="2" t="n">
         <v>1.087682343522149</v>
       </c>
-      <c r="K117" s="2" t="n">
+      <c r="K118" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" s="2" t="n">
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
         <v>0.1127536980111381</v>
       </c>
-      <c r="O117" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq6_2026-08-27.xlsx
+++ b/output/full_scan/batch_seq6_2026-08-27.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6474</v>
+        <v>6217</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>959.1750447155828</v>
+        <v>1077.643509881708</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>40.35</v>
+        <v>177.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.10940154524361</v>
+        <v>55.70252314922136</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15.29876028105093</v>
+        <v>13.7548524043765</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.017504471558263</v>
+        <v>2.367600546422464</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0403416876626349</v>
+        <v>4.616779734730082</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6217</v>
+        <v>6187</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>877.6435098817084</v>
+        <v>1062.499639912853</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>177.5</v>
+        <v>1430</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>55.70252314417844</v>
+        <v>64.75681222531871</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13.75485228198902</v>
+        <v>21.71856829855759</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.367600546422464</v>
+        <v>1.349963991285267</v>
       </c>
       <c r="K3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>4.616779734949485</v>
+        <v>14.75966093595285</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6187</v>
+        <v>6269</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>862.4996399128527</v>
+        <v>1022.060969395345</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1430</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,29 +658,29 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.7568122223918</v>
+        <v>66.79925622957137</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>21.71856826387475</v>
+        <v>17.30563503158836</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.349963991285267</v>
+        <v>2.988153589909007</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>14.75966093757469</v>
+        <v>0.7134549076143746</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>821.633461511159</v>
+        <v>1021.633461511159</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>250.5</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>59.24899814522393</v>
+        <v>59.24899816643475</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>25.57474896621512</v>
+        <v>25.57474907032129</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>1.763346151115898</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>6.472562942134863</v>
+        <v>6.472562941600655</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6183</v>
+        <v>6278</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>783.8860812236328</v>
+        <v>979.9001866752676</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>206</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>62.07136716740992</v>
+        <v>66.80407268185999</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>38.30206499794927</v>
+        <v>18.78033465025939</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.551560028254277</v>
+        <v>2.590018667526751</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0520407686255198</v>
+        <v>4.711998880506076</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6291</v>
+        <v>6474</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>780.7896100338492</v>
+        <v>959.1750447155828</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>417</v>
+        <v>40.35</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.10363411874179</v>
+        <v>63.10940149654919</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>17.04959454072975</v>
+        <v>15.29876028105093</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.188623055302946</v>
+        <v>4.017504471558263</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>7.752249654629184</v>
+        <v>0.0403416879488275</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6164</v>
+        <v>6291</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>751.0459314584523</v>
+        <v>950.7896100338492</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12.55</v>
+        <v>417</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>56.78272552987154</v>
+        <v>56.10363412015371</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.38779721764997</v>
+        <v>17.04959454823939</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.340058698825225</v>
+        <v>2.188623055302946</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1290095038231747</v>
+        <v>7.752249654533767</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6190</v>
+        <v>6168</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>735.0559310146091</v>
+        <v>935.1586960392348</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>68.8</v>
+        <v>29.65</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>51.23552012582814</v>
+        <v>68.77111252858192</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>26.02241105564243</v>
+        <v>16.67584763418724</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.721289505641604</v>
+        <v>3.124533840388274</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.6613388461673289</v>
+        <v>0.6716190247616078</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6416</v>
+        <v>6226</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>728.425593609236</v>
+        <v>922.4677380282332</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>101.5</v>
+        <v>30.95</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.39883817070087</v>
+        <v>74.12762839636667</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15.16820916188202</v>
+        <v>23.85900845683471</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.4542799172824589</v>
+        <v>1.346773802823326</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0525889953223375</v>
+        <v>0.9750166605931588</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6426</v>
+        <v>6164</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>728.0099165070362</v>
+        <v>921.0459314584524</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>259.5</v>
+        <v>12.55</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>66.08210019218168</v>
+        <v>56.78272549124004</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>31.53057506618581</v>
+        <v>22.38779723492217</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.176378009645191</v>
+        <v>2.340058698825225</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>4.62465086355054</v>
+        <v>0.1290095038231747</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6214</v>
+        <v>6418</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>727.7962317862725</v>
+        <v>909</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>182.5</v>
+        <v>37.15</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>76.8035950174006</v>
+        <v>69.43320408033303</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>34.1630062170431</v>
+        <v>23.13697410932746</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.6125741029190068</v>
+        <v>5.295665181323336</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.639907757447396</v>
+        <v>0.4077749073582894</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6168</v>
+        <v>6190</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>725.1586960392348</v>
+        <v>875.0559310146091</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>29.65</v>
+        <v>68.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>68.7711124947504</v>
+        <v>51.23552013979413</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>16.67584748454084</v>
+        <v>26.02241107319101</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.124533840388274</v>
+        <v>1.721289505641604</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,11 +1153,11 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.6716190248474645</v>
+        <v>0.6613388460337788</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>724.201161159354</v>
+        <v>864.2011611593541</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>46.4</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>58.50182217797105</v>
+        <v>58.50182220966192</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>19.49412373749283</v>
+        <v>19.49412379291364</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>3.836984657479373</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.3660771011838037</v>
+        <v>0.3660771010502427</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6418</v>
+        <v>6205</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>709</v>
+        <v>849.0895100557981</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>37.15</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>69.43320407874793</v>
+        <v>60.3228187204425</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>23.13697410505026</v>
+        <v>16.39256585304434</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5.295665181323336</v>
+        <v>4.271252381236805</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.4077749073487493</v>
+        <v>0.9317867395905248</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6226</v>
+        <v>6446</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>702.4677380282333</v>
+        <v>833.572711750798</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>30.95</v>
+        <v>1560</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>74.1276283900424</v>
+        <v>65.7332955343995</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>23.85900851188285</v>
+        <v>35.94501794326504</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.346773802823326</v>
+        <v>0.9906350441492636</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.9750166606255946</v>
+        <v>14.48042024756323</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6456</v>
+        <v>6426</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>701.4609871156276</v>
+        <v>828.0099165070362</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>71.8</v>
+        <v>259.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>58.707617397876</v>
+        <v>66.0821002066387</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>14.30121053416348</v>
+        <v>31.53057512885547</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.682616117344707</v>
+        <v>2.176378009645191</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.7687075501953375</v>
+        <v>4.624650862882747</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6269</v>
+        <v>6456</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>692.0609693953451</v>
+        <v>801.4609871156275</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>66.79925622663498</v>
+        <v>58.70761740259806</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>17.30563486094415</v>
+        <v>14.30121053490165</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.988153589909007</v>
+        <v>1.682616117344707</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.7134549078433273</v>
+        <v>0.7687075500426972</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6259</v>
+        <v>6213</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>679.9145880322792</v>
+        <v>801.4035350147216</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>30.25</v>
+        <v>563</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>46.33771650857991</v>
+        <v>72.23704398901592</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10.00900939132233</v>
+        <v>29.42663292501877</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.3364274028687954</v>
+        <v>2.025322841391783</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.0226923419332322</v>
+        <v>10.21029620144291</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6205</v>
+        <v>6183</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>679.0895100557981</v>
+        <v>783.8860812236328</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>60.32281875109746</v>
+        <v>62.07136720706762</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>16.39256581976119</v>
+        <v>38.30206499794927</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>4.271252381236805</v>
+        <v>2.551560028254277</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.931786739867176</v>
+        <v>0.0520407686255198</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6263</v>
+        <v>6209</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>675.9235032557176</v>
+        <v>776.8906658946066</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>165.5</v>
+        <v>76.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>59.55245338322878</v>
+        <v>57.74780399922693</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>11.69901263439345</v>
+        <v>12.58498428166035</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7618148833414132</v>
+        <v>4.218720032561902</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.7000150507666207</v>
+        <v>0.7949788325551965</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6278</v>
+        <v>6449</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>664.9001866752675</v>
+        <v>770.9430878188858</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>66.80407264811018</v>
+        <v>47.93277183839593</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>18.7803346502594</v>
+        <v>26.15572370037608</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.590018667526751</v>
+        <v>1.988626311644872</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,11 +1630,11 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>4.711998881078458</v>
+        <v>2.734776333155478</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>652.3569911159263</v>
+        <v>767.3569911159263</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>49.1</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>65.21686416454054</v>
+        <v>65.21686399758892</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>22.2908587903731</v>
+        <v>22.2908588334092</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1.32320733149964</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.3239423878866051</v>
+        <v>0.3239423879247664</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6213</v>
+        <v>6224</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>631.4035350147216</v>
+        <v>746.1445493945221</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>563</v>
+        <v>76.2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>72.23704398801925</v>
+        <v>64.6870267022005</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>29.42663295852862</v>
+        <v>31.7533549119586</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.025322841391783</v>
+        <v>1.045227467565479</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>10.21029620171004</v>
+        <v>2.324814524769593</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6225</v>
+        <v>6416</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>627.2039179184864</v>
+        <v>738.425593609236</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>66</v>
+        <v>101.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>78.97154865841232</v>
+        <v>56.39883821096321</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>51.71079623557296</v>
+        <v>15.16820921793563</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7006511843128723</v>
+        <v>0.4542799172824589</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>2.909825532127702</v>
+        <v>0.0525889947881152</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6279</v>
+        <v>6214</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>619.9436244333374</v>
+        <v>727.7962317862725</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>127.5</v>
+        <v>182.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>59.04968579840885</v>
+        <v>76.80359503426543</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>16.78416993460167</v>
+        <v>34.16300622139386</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4899068183922407</v>
+        <v>0.6125741029190068</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.1527243131508964</v>
+        <v>1.639907757352011</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6224</v>
+        <v>6207</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>616.1445493945221</v>
+        <v>727.5606488634621</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>76.2</v>
+        <v>108</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>64.68702671963624</v>
+        <v>49.19478425612196</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>31.75335490554575</v>
+        <v>14.51022023371729</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.045227467565479</v>
+        <v>1.953728735713992</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>2.324814524864979</v>
+        <v>1.39534964914523</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6449</v>
+        <v>6227</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>615.9430878188858</v>
+        <v>709.6272897740486</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>233</v>
+        <v>125</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>47.93277185148385</v>
+        <v>57.60418481492205</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.15572363579692</v>
+        <v>10.92577439193357</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.988626311644872</v>
+        <v>3.757913390799154</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>2.734776333346282</v>
+        <v>-0.1946381083060868</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6446</v>
+        <v>6204</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>613.5727117507979</v>
+        <v>702.1088849843521</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1560</v>
+        <v>89</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>65.73329553173532</v>
+        <v>57.90420057648694</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>35.94501790994922</v>
+        <v>17.63181575900663</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.9906350441492636</v>
+        <v>1.583222198151214</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>14.48042025023459</v>
+        <v>1.410268942869537</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6175</v>
+        <v>6271</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>602.8561678490728</v>
+        <v>699.640576877585</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>74.2</v>
+        <v>210</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>41.26765258094702</v>
+        <v>57.77445494340788</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.55618893748282</v>
+        <v>13.73868668913188</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.188679943886496</v>
+        <v>1.085053326754367</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.5730590885676747</v>
+        <v>3.407047478218561</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6419</v>
+        <v>6265</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>590.2994230566159</v>
+        <v>698.2488067734529</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>154</v>
+        <v>58.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>52.10969393383017</v>
+        <v>54.84000296804222</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>23.034675476047</v>
+        <v>23.29603476287756</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.2762133967014958</v>
+        <v>0.5262346521909952</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.722939978493053</v>
+        <v>0.0307565883061582</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6207</v>
+        <v>6236</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>587.5606488634621</v>
+        <v>695.1827363193779</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>108</v>
+        <v>17.45</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>49.19478427276558</v>
+        <v>58.56596814255006</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>14.51022021466858</v>
+        <v>10.62038184111301</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.953728735713992</v>
+        <v>2.958085597759324</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1.395349649326484</v>
+        <v>1.057162494045102</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6265</v>
+        <v>6218</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>583.2488067734528</v>
+        <v>690.8880938607822</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>58.1</v>
+        <v>39.95</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>54.84000297065366</v>
+        <v>64.20730583659677</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23.29603475347119</v>
+        <v>29.3210587931605</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5262346521909952</v>
+        <v>1.412731249670584</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0307565883023435</v>
+        <v>0.4797221306016787</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6227</v>
+        <v>6259</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>569.6272897740486</v>
+        <v>679.9145880322792</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>125</v>
+        <v>30.25</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>57.60418484480008</v>
+        <v>46.33771649062469</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>10.92577436502908</v>
+        <v>10.00900937568997</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>3.757913390799154</v>
+        <v>0.3364274028687954</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.1946381079626531</v>
+        <v>0.0226923419332322</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6173</v>
+        <v>6263</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>567.0426198422796</v>
+        <v>675.9235032557176</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>217.5</v>
+        <v>165.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>55.09351969529265</v>
+        <v>59.55245333029796</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>18.14151412871825</v>
+        <v>11.69901269285025</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.8130526955699633</v>
+        <v>0.7618148833414132</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>3.93273239842955</v>
+        <v>0.700015050575844</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6220</v>
+        <v>6477</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>563.372972791782</v>
+        <v>674.333379586995</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>26.05</v>
+        <v>38.15</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>43.41569951833669</v>
+        <v>55.61136156310334</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23.95220842503576</v>
+        <v>18.48550012638493</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.997626275286056</v>
+        <v>1.742901877643565</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3035432889210363</v>
+        <v>0.102648167444466</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6204</v>
+        <v>6472</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>562.1088849843521</v>
+        <v>644.6290875051347</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>89</v>
+        <v>439.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>57.90420055172869</v>
+        <v>54.86766632774048</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>17.63181575900663</v>
+        <v>30.38230271746542</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.583222198151214</v>
+        <v>1.250456044578128</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.410268942793219</v>
+        <v>3.782835632833256</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6271</v>
+        <v>6167</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>559.6405768775849</v>
+        <v>639.3082357857987</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>210</v>
+        <v>10.95</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>57.77445494340788</v>
+        <v>56.33917278644567</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>13.73868661136515</v>
+        <v>13.58031167344346</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.085053326754367</v>
+        <v>2.066901738352045</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>3.407047478600147</v>
+        <v>0.0836929353962966</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6477</v>
+        <v>6225</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>554.333379586995</v>
+        <v>627.2039179184864</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>38.15</v>
+        <v>66</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>55.61136155802543</v>
+        <v>78.97154865841232</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>18.48550009284065</v>
+        <v>51.71079623557296</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.742901877643565</v>
+        <v>0.7006511843128723</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1026481675589435</v>
+        <v>2.909825532127702</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6218</v>
+        <v>6279</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>550.8880938607831</v>
+        <v>619.9436244333374</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>39.95</v>
+        <v>127.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>64.20730582233293</v>
+        <v>59.04968582037586</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>29.32105875101879</v>
+        <v>16.78416998120526</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.412731249670584</v>
+        <v>0.4899068183922407</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>1</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.4797221306493732</v>
+        <v>-0.1527243135324889</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6209</v>
+        <v>6405</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>546.8906658946066</v>
+        <v>618.9915540852727</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>76.5</v>
+        <v>40.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>57.74780399107588</v>
+        <v>46.8682150125765</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>12.58498418542916</v>
+        <v>25.565627038746</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4.218720032561902</v>
+        <v>2.720820688350131</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.7949788326792024</v>
+        <v>0.8469139490905113</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6292</v>
+        <v>6241</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>532.4064531380038</v>
+        <v>613.4456595402743</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>61.4</v>
+        <v>17.65</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>54.29346851321301</v>
+        <v>62.86274644958372</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25.44755726582328</v>
+        <v>23.50731987834651</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.2492627180621283</v>
+        <v>0.5305995190106255</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.1799907604365214</v>
+        <v>0.1578683931952808</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6277</v>
+        <v>6175</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>529.9491391413443</v>
+        <v>602.8561678490728</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.52475387071584</v>
+        <v>41.26765258490371</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>38.11826004969415</v>
+        <v>20.5561890318981</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3610831226172822</v>
+        <v>1.188679943886496</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.4344851379595196</v>
+        <v>0.5730590884341185</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6472</v>
+        <v>6237</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>529.6290875051349</v>
+        <v>594.5766006633116</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>439.5</v>
+        <v>34.8</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>54.86766630403056</v>
+        <v>48.66729024730013</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>30.38230269846272</v>
+        <v>24.08243173883129</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.250456044578128</v>
+        <v>1.052384629266402</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>3.782835635504359</v>
+        <v>0.4098674114800544</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6167</v>
+        <v>6409</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>524.3082357857987</v>
+        <v>593.1542752639602</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>10.95</v>
+        <v>1045</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>56.33917265092089</v>
+        <v>55.23274965078696</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>13.58031164978954</v>
+        <v>19.65360594889947</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.066901738352045</v>
+        <v>0.9328637152552608</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.08369293551074269</v>
+        <v>3.506091263701782</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6206</v>
+        <v>6285</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>512.7462204348402</v>
+        <v>592.8633711599275</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>140.5</v>
+        <v>245</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.19044376557444</v>
+        <v>51.42364076322657</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>25.2017912412354</v>
+        <v>15.72068173900475</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.210503597914283</v>
+        <v>1.441675688707351</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-1.047102464895671</v>
+        <v>0.4444313772197246</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6411</v>
+        <v>6419</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>511.520797953779</v>
+        <v>590.2994230566159</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>79.5</v>
+        <v>154</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>48.4789791021649</v>
+        <v>52.10969393183165</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.73423693336333</v>
+        <v>23.03467547604699</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7061657539267587</v>
+        <v>0.2762133967014958</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.7755235421660407</v>
+        <v>-0.7229399787029331</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6405</v>
+        <v>6423</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>503.9915540852726</v>
+        <v>581.7477478870816</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>40.3</v>
+        <v>81.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>46.86821500703356</v>
+        <v>58.38527330539568</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25.56562698625925</v>
+        <v>15.77293628740233</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.720820688350131</v>
+        <v>0.5016471369601443</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,11 +3008,11 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.8469139491572855</v>
+        <v>0.4093047322556724</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>503.8439881848532</v>
+        <v>575.9639777623507</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>77.90000000000001</v>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>46.46371559568259</v>
+        <v>46.46371564355972</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>29.42616229105386</v>
+        <v>29.4261622262368</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.1761905985981869</v>
+        <v>2.456125606013882</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0332550224547008</v>
+        <v>0.03325502241654</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6245</v>
+        <v>6173</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>502.7549792503377</v>
+        <v>567.0426198422796</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>83.7</v>
+        <v>217.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.94250361124868</v>
+        <v>55.09351969734079</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>11.804463595152</v>
+        <v>18.14151421510043</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6211457646041798</v>
+        <v>0.8130526955699633</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.1783725182669137</v>
+        <v>3.932732398257836</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6236</v>
+        <v>6220</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>495.182736319378</v>
+        <v>563.372972791782</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>17.45</v>
+        <v>26.05</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>58.56596814255006</v>
+        <v>43.41569956789709</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10.62038184111301</v>
+        <v>23.95220845773247</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.958085597759324</v>
+        <v>1.997626275286056</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>1.057162494045102</v>
+        <v>0.3035432888542551</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6174</v>
+        <v>6234</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>492.1005043823594</v>
+        <v>563.0434622324619</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>45</v>
+        <v>36.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>49.88767601462276</v>
+        <v>50.60478442415916</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13.8071958810746</v>
+        <v>20.38830968024011</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4415430825736443</v>
+        <v>0.7875833728851465</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.5102549492006965</v>
+        <v>0.3854288374564092</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6409</v>
+        <v>6415</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>483.1542752639603</v>
+        <v>549.4932896796429</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1045</v>
+        <v>470.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>55.23274969979514</v>
+        <v>52.89431909339655</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.65360594889947</v>
+        <v>11.57550923229222</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.9328637152552608</v>
+        <v>1.504359538454384</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>3.506091267517757</v>
+        <v>5.401502465908182</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6237</v>
+        <v>6202</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>479.5766006633116</v>
+        <v>540.6935757623623</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>34.8</v>
+        <v>59.2</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>48.66729025095434</v>
+        <v>50.80058849124863</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.08243162372197</v>
+        <v>14.21170926317898</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.052384629266402</v>
+        <v>0.462088409530997</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.4098674116422378</v>
+        <v>-0.0065635409795546</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6285</v>
+        <v>6435</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>477.8633711599276</v>
+        <v>537.2931534962586</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>245</v>
+        <v>263.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.42364073050402</v>
+        <v>48.91089931595389</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>15.72068173049982</v>
+        <v>16.6792613883983</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.441675688707351</v>
+        <v>0.9116730723680584</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.4444313776967163</v>
+        <v>3.11161797568373</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6423</v>
+        <v>6451</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>466.7477478870817</v>
+        <v>532.5621086837976</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>81.5</v>
+        <v>452</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>58.3852732908355</v>
+        <v>52.67442736257749</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>15.77293628376656</v>
+        <v>11.06855917197468</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5016471369601443</v>
+        <v>2.354567906675494</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.4093047323129173</v>
+        <v>5.769307951442865</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6234</v>
+        <v>6292</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>448.0434622324622</v>
+        <v>532.4064531380038</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>36.7</v>
+        <v>61.4</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.60478449833932</v>
+        <v>54.29346851321301</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>20.3883096312268</v>
+        <v>25.44755734626092</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.7875833728851465</v>
+        <v>0.2492627180621283</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.3854288373037744</v>
+        <v>-0.1799907604937678</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6177</v>
+        <v>6277</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>441.2150731922997</v>
+        <v>529.9491391413443</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>47.9</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.54912985028621</v>
+        <v>51.52475385162062</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>22.94132681441765</v>
+        <v>38.11826006253359</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4720709233914665</v>
+        <v>0.3610831226172822</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.06870463492030519</v>
+        <v>-0.4344851379785932</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6261</v>
+        <v>6176</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>430.1184819491936</v>
+        <v>526.0324060787623</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>46.36580918176321</v>
+        <v>59.66101214388141</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>25.92182320182519</v>
+        <v>28.6530468702594</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.506080184892399</v>
+        <v>0.5234988317811624</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.9191747330913153</v>
+        <v>1.844988150888602</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6435</v>
+        <v>6438</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>422.2931534962585</v>
+        <v>519.9398229458798</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>263.5</v>
+        <v>148.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.9108993047255</v>
+        <v>54.09505367231951</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16.67926137049172</v>
+        <v>14.61139484961314</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.9116730723680584</v>
+        <v>1.391438176272748</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>3.111617975931788</v>
+        <v>0.7093799723705796</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6274</v>
+        <v>6206</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>417.5657394699555</v>
+        <v>512.7462204348402</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>1445</v>
+        <v>140.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>48.56786889892033</v>
+        <v>51.1904437880492</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>12.83901427558343</v>
+        <v>25.20179130614143</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.670890294545647</v>
+        <v>0.210503597914283</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-5.569464528645415</v>
+        <v>-1.047102464991096</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6462</v>
+        <v>6163</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>416.2878771992283</v>
+        <v>511.7659261139766</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>100.5</v>
+        <v>43.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>49.66217448186525</v>
+        <v>52.52454473928551</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>12.30910157210796</v>
+        <v>16.41708055433545</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.9279941371553924</v>
+        <v>0.5406219643915496</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.6338987431576795</v>
+        <v>0.2778153690280554</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6241</v>
+        <v>6197</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>413.4456595402743</v>
+        <v>511.7584122339106</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>17.65</v>
+        <v>308</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>62.86274637725741</v>
+        <v>51.57481325480898</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.50731982285693</v>
+        <v>16.93669460755283</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5305995190106255</v>
+        <v>0.8632581620304356</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1578683933074181</v>
+        <v>1.371344228821135</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6182</v>
+        <v>6411</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>411.3810800793126</v>
+        <v>511.520797953779</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>109</v>
+        <v>79.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.405613735839</v>
+        <v>48.47897908565256</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.946332214277</v>
+        <v>15.7342369354124</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.7614642569505581</v>
+        <v>0.7061657539267587</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.9068437701025488</v>
+        <v>0.7755235421087927</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6415</v>
+        <v>6245</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>409.4932896796428</v>
+        <v>502.7549792503377</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>470.5</v>
+        <v>83.7</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.89431911582091</v>
+        <v>52.94250366183044</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>11.57550923686913</v>
+        <v>11.80446372511852</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.504359538454384</v>
+        <v>0.6211457646041798</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>5.401502466671408</v>
+        <v>-0.1783725187438992</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6257</v>
+        <v>6174</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>407.2974192789693</v>
+        <v>492.1005043823594</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>204</v>
+        <v>45</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>48.32270896471538</v>
+        <v>49.88767601945005</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13.63350909383357</v>
+        <v>13.80719603889484</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.048898270038403</v>
+        <v>0.4415430825736443</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.8679822622059099</v>
+        <v>0.510254949181618</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6284</v>
+        <v>6230</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>399.2339417410342</v>
+        <v>483.138976899541</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>77.8</v>
+        <v>110</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,49 +3997,49 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>47.34805502749926</v>
+        <v>47.74197211303397</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>17.93524215243008</v>
+        <v>17.34195736150842</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6406584815951419</v>
+        <v>1.032044973379868</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.7878930366212047</v>
+        <v>0.6400649095202757</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6163</v>
+        <v>6210</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>396.7659261139754</v>
+        <v>471.0873381660404</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>43.5</v>
+        <v>18.05</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>52.52454476483901</v>
+        <v>51.5932367200336</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16.41708056395844</v>
+        <v>7.214161890273215</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5406219643915496</v>
+        <v>0.5076540552056265</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.2778153689803602</v>
+        <v>0.1332385890910914</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6197</v>
+        <v>6243</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>396.7584122339106</v>
+        <v>461.0875492540233</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>308</v>
+        <v>42.4</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.57481322686467</v>
+        <v>45.64990556097909</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16.93669458323245</v>
+        <v>21.33420501917555</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8632581620304356</v>
+        <v>0.8411972101145833</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>1.371344228821135</v>
+        <v>-0.6039907153852647</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6222</v>
+        <v>6442</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>391.2928265074708</v>
+        <v>451.6153555149217</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>20.05</v>
+        <v>1595</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>51.33754291450627</v>
+        <v>56.14422542211476</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>9.542448887721989</v>
+        <v>19.48694402570913</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.558260869565217</v>
+        <v>1.035913548167035</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.3947351962220311</v>
+        <v>18.62131201728168</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6223</v>
+        <v>6235</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>382.7808960641328</v>
+        <v>443.959865629963</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>5090</v>
+        <v>39.2</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>39.72950634196207</v>
+        <v>52.33936310843332</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>16.46405393240086</v>
+        <v>12.43646806631544</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2.707756815021831</v>
+        <v>1.130150567078948</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-83.91010771860903</v>
+        <v>0.1474686831150337</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6432</v>
+        <v>6239</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>380.0869665702022</v>
+        <v>438.5935762129211</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>63.8</v>
+        <v>277</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>40.11821467171292</v>
+        <v>50.44797766256402</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.80699288712254</v>
+        <v>13.06348012913197</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.3557522000982056</v>
+        <v>1.828117005366576</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.9598406854172126</v>
+        <v>2.673981811041469</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6270</v>
+        <v>6177</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>374.9811075460765</v>
+        <v>431.2150731922997</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>29.85</v>
+        <v>47.9</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.7570620948402</v>
+        <v>51.54912984052692</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>10.17317689956134</v>
+        <v>22.94132686347236</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5273306182755232</v>
+        <v>0.4720709233914665</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.115678866244644</v>
+        <v>-0.06870463492030519</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6412</v>
+        <v>6261</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>363.8788256535523</v>
+        <v>430.1184819491936</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>78.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>44.82111871226887</v>
+        <v>46.36580918723233</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>26.17836525442699</v>
+        <v>25.92182322775525</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.8802268033480223</v>
+        <v>1.506080184892399</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.3808067578329461</v>
+        <v>0.9191747329959128</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6210</v>
+        <v>6274</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>356.0873381660404</v>
+        <v>417.5657394699555</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>18.05</v>
+        <v>1445</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>51.59323522322114</v>
+        <v>48.56786889050278</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>7.214157647123484</v>
+        <v>12.8390141874175</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5076540552056265</v>
+        <v>1.670890294545647</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.133238592429993</v>
+        <v>-5.569464527691594</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6215</v>
+        <v>6233</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>354.6830957104912</v>
+        <v>417.2200536865566</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>98.2</v>
+        <v>21.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.49997437552162</v>
+        <v>50.97364237328794</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13.6857421727666</v>
+        <v>15.94022637700339</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.776926693389151</v>
+        <v>1.205275836698622</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0115312419453571</v>
+        <v>0.1679327421781106</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6283</v>
+        <v>6462</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>354.575481055815</v>
+        <v>416.2878771992283</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>20.1</v>
+        <v>100.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>42.55727797931045</v>
+        <v>49.66217486215629</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>32.34792396577512</v>
+        <v>12.3091016025902</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7868733491177492</v>
+        <v>0.9279941371553924</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1029767385301622</v>
+        <v>0.6338987421083129</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6451</v>
+        <v>6182</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>342.5621086837976</v>
+        <v>411.3810800793126</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>452</v>
+        <v>109</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>52.67442735688263</v>
+        <v>48.40561373627979</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>11.06855917197467</v>
+        <v>12.94633226786353</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2.354567906675494</v>
+        <v>0.7614642569505581</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>5.769307952778412</v>
+        <v>0.9068437699594464</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6243</v>
+        <v>6257</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>341.0875492540233</v>
+        <v>407.2974192789693</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>42.4</v>
+        <v>204</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45.64990551788802</v>
+        <v>48.32270891403445</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>21.3342048966339</v>
+        <v>13.63350911302534</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.8411972101145833</v>
+        <v>1.048898270038403</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.6039907151181529</v>
+        <v>0.8679822623776428</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6239</v>
+        <v>6284</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>338.5935762129211</v>
+        <v>399.2339417410342</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>277</v>
+        <v>77.8</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,49 +4686,49 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>50.44797765957119</v>
+        <v>47.34805503779151</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13.06348012913197</v>
+        <v>17.9352421861781</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.828117005366576</v>
+        <v>0.6406584815951419</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>2.67398181142308</v>
+        <v>0.7878930362968708</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6441</v>
+        <v>6222</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>337.6008368352781</v>
+        <v>391.2928265074708</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>21.5</v>
+        <v>20.05</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>48.89728003579422</v>
+        <v>51.33754290463593</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>21.41414918172828</v>
+        <v>9.542449048413779</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2616427149097757</v>
+        <v>1.558260869565217</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.029514104023495</v>
+        <v>0.3947351961838715</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6442</v>
+        <v>6223</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>336.6153555149216</v>
+        <v>384.6812395958795</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>1595</v>
+        <v>5090</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>56.14422540837855</v>
+        <v>39.7295063313155</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>19.48694395073623</v>
+        <v>16.46405386094304</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.035913548167035</v>
+        <v>2.818262834889745</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>18.62131202042988</v>
+        <v>-83.91010771383958</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6185</v>
+        <v>6412</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>332.1493691332566</v>
+        <v>383.8788256535523</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>12.6</v>
+        <v>78.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,49 +4845,49 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>27.85960369995605</v>
+        <v>44.82111915643832</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>24.03047589966277</v>
+        <v>26.17836525442697</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.614936913325661</v>
+        <v>0.8802268033480223</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0756532890507932</v>
+        <v>0.3808067577375571</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6202</v>
+        <v>6443</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>330.6935757623624</v>
+        <v>381.5286339874146</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>59.2</v>
+        <v>26.7</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>50.80058845836269</v>
+        <v>46.12569209493901</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>14.21170925650396</v>
+        <v>13.97820323975086</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.462088409530997</v>
+        <v>1.073197041426991</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0065635406933595</v>
+        <v>0.2820054224662396</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6196</v>
+        <v>6432</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>327.0100445302024</v>
+        <v>380.0869665702022</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>497.5</v>
+        <v>63.8</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>47.9823830350018</v>
+        <v>40.11821466890378</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11.11310049499699</v>
+        <v>13.80699282028023</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.7129006246195684</v>
+        <v>0.3557522000982056</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.445461931741745</v>
+        <v>-0.9598406854267464</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6443</v>
+        <v>6270</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>306.5286339874146</v>
+        <v>374.9811075460765</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>26.7</v>
+        <v>29.85</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>46.12569207532155</v>
+        <v>46.7570620984746</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13.97820324574174</v>
+        <v>10.17317685349816</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.073197041426991</v>
+        <v>0.5273306182755232</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.2820054225425572</v>
+        <v>0.1156788661969503</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6194</v>
+        <v>6215</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>306.2616040346652</v>
+        <v>374.6830957104913</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>29.7</v>
+        <v>98.2</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>43.64268065368359</v>
+        <v>47.49997438019586</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>24.41041040372549</v>
+        <v>13.68574229803762</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.1054718327369433</v>
+        <v>0.776926693389151</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0845102708061579</v>
+        <v>-0.011531242899329</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6233</v>
+        <v>6283</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>302.2200536865566</v>
+        <v>354.575481055815</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>21.8</v>
+        <v>20.1</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>50.97364237328794</v>
+        <v>42.5572781163298</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15.94022633579221</v>
+        <v>32.34792399408956</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.205275836698622</v>
+        <v>0.7868733491177492</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1679327422925859</v>
+        <v>0.1029767385015467</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6266</v>
+        <v>6441</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>299.9486676355761</v>
+        <v>337.6008368352781</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>25.15</v>
+        <v>21.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>52.95215356364288</v>
+        <v>48.897280137643</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.13186873237317</v>
+        <v>21.41414921916029</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5632081787254587</v>
+        <v>0.2616427149097757</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0716904234979009</v>
+        <v>-0.0295141042429079</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6184</v>
+        <v>6185</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>298.595202077796</v>
+        <v>332.1493691332566</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>41.45</v>
+        <v>12.6</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>25.70490976134264</v>
+        <v>27.85960392582068</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>22.0271439913321</v>
+        <v>24.03047595275491</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.714082424674679</v>
+        <v>1.614936913325661</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0109087182239371</v>
+        <v>-0.075653289127111</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5244,21 +5244,21 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6191</v>
+        <v>6196</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>295.5134663406052</v>
+        <v>327.0100445302032</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>83.09999999999999</v>
+        <v>497.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>42.43589944184029</v>
+        <v>47.98238302434173</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>28.35698755825117</v>
+        <v>11.11310045869096</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6175619092646252</v>
+        <v>0.7129006246195684</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.2312574428318838</v>
+        <v>0.4454619315509829</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6438</v>
+        <v>6191</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>294.9398229458806</v>
+        <v>315.5134663406052</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>148.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,49 +5322,49 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>54.0950537516324</v>
+        <v>42.43589952198354</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>14.61139483065855</v>
+        <v>28.35698756891997</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.391438176272748</v>
+        <v>0.6175619092646252</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.7093799741831008</v>
+        <v>0.2312574427555644</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6188</v>
+        <v>6272</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>289.4250125644558</v>
+        <v>310.2513363168909</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>69.5</v>
+        <v>24.1</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46.46081531562713</v>
+        <v>43.90364430863304</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>19.31392010626888</v>
+        <v>43.09913342202094</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.24785832686515</v>
+        <v>0.6664597938358339</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.1124620267970446</v>
+        <v>0.2425426743794474</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6465</v>
+        <v>6194</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>288.7581533450913</v>
+        <v>306.2616040346652</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>46.5</v>
+        <v>29.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>40.83122274378279</v>
+        <v>43.64268073310201</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>15.68924954906356</v>
+        <v>24.41041039751517</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5717348434761482</v>
+        <v>0.1054718327369433</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.3097472066034967</v>
+        <v>0.0845102707489159</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6244</v>
+        <v>6266</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>284.6909788910033</v>
+        <v>299.948667635576</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>24.25</v>
+        <v>25.15</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>46.38699058333941</v>
+        <v>52.95215356364288</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>16.94462102383009</v>
+        <v>11.13186872724505</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8705085415261173</v>
+        <v>0.5632081787254587</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0620406198686276</v>
+        <v>0.0716904234883616</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6229</v>
+        <v>6184</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>281.0060042406503</v>
+        <v>298.5952020777962</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>23.7</v>
+        <v>41.45</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>47.48562221587743</v>
+        <v>25.70490980221196</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.88403924106945</v>
+        <v>22.02714401818274</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4808698652998647</v>
+        <v>1.714082424674679</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,51 +5552,51 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.07002096276364909</v>
+        <v>0.0109087181666945</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6288</v>
+        <v>6188</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>274.3107407686553</v>
+        <v>289.4250125644558</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>20.95</v>
+        <v>69.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G97" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.58025174415962</v>
+        <v>46.46081539278499</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v/>
+        <v>19.31392011402933</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6831032524092705</v>
+        <v>1.24785832686515</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0313138023965832</v>
+        <v>0.1124620263963702</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6192</v>
+        <v>6465</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>271.8466635641981</v>
+        <v>288.7581533450913</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>116.5</v>
+        <v>46.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>50.26657100814429</v>
+        <v>40.83122298069858</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.25888653556222</v>
+        <v>15.68924957563691</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6516026687772569</v>
+        <v>0.5717348434761482</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.1307261474343863</v>
+        <v>0.3097472065217452</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6166</v>
+        <v>6244</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>268.4629016056404</v>
+        <v>284.6909788910033</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>117</v>
+        <v>24.25</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>40.53505840017748</v>
+        <v>46.38699061505462</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.68752514661066</v>
+        <v>16.94462101552469</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.381200983077805</v>
+        <v>0.8705085415261173</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-1.551636894933722</v>
+        <v>0.0620406198018492</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6230</v>
+        <v>6276</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>258.138976899541</v>
+        <v>283.8404928386959</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>110</v>
+        <v>20.2</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>47.74197206575581</v>
+        <v>49.48054252760596</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.34195735733286</v>
+        <v>23.49337296211367</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.032044973379868</v>
+        <v>1.041598882020045</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.6400649102834626</v>
+        <v>0.2336167449170451</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6165</v>
+        <v>6229</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>257.7706098297474</v>
+        <v>281.0060042406503</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>48.05</v>
+        <v>23.7</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46.58796104624594</v>
+        <v>47.48562212594499</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10.36457893632072</v>
+        <v>13.88403927066213</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.2855957190680591</v>
+        <v>0.4808698652998647</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,51 +5817,51 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0792275003523573</v>
+        <v>0.0700209628304259</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6198</v>
+        <v>6288</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>257.1133611480075</v>
+        <v>274.1623227954031</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>19.65</v>
+        <v>20.95</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="G102" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>51.66509908412941</v>
+        <v>45.12010230369736</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>5.957647626643677</v>
+        <v/>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.0643979866376591</v>
+        <v>0.6831032524092705</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.2411182515691116</v>
+        <v>0.0137243745044277</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6414</v>
+        <v>6192</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>254.160789194872</v>
+        <v>271.8466635641981</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>393.5</v>
+        <v>116.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>42.61736116223893</v>
+        <v>50.26657101608465</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.44892894712812</v>
+        <v>18.25888655633903</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.3337297340452832</v>
+        <v>0.6516026687772569</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-6.19518429024724</v>
+        <v>0.1307261473199081</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6176</v>
+        <v>6166</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>251.0324060787623</v>
+        <v>268.4629016056405</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>95.5</v>
+        <v>117</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>59.66101200826864</v>
+        <v>40.53505840992981</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>28.65304687025939</v>
+        <v>15.68752522795294</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5234988317811624</v>
+        <v>0.381200983077805</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>1.844988151706069</v>
+        <v>-1.551636895143581</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6417</v>
+        <v>6165</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>248.0022481125078</v>
+        <v>257.7706098297474</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>106</v>
+        <v>48.05</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>36.25788612758365</v>
+        <v>46.5879609258403</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>24.44116475386731</v>
+        <v>10.3645789218238</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4984329999839432</v>
+        <v>0.2855957190680591</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.1360725682071941</v>
+        <v>-0.0792275003523573</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6208</v>
+        <v>6198</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>231.7194974185409</v>
+        <v>257.1133611480075</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>19.65</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>48.75243338606559</v>
+        <v>51.66509909599426</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>8.855367031229179</v>
+        <v>5.957647628901794</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4538354739187082</v>
+        <v>0.0643979866376591</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.378649152576834</v>
+        <v>0.2411182514450931</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6246</v>
+        <v>6414</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>230.018922356671</v>
+        <v>254.160789194872</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>12.55</v>
+        <v>393.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45.65471028113036</v>
+        <v>42.61736113186489</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>20.53521366576993</v>
+        <v>18.44892897500064</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3358940919900492</v>
+        <v>0.3337297340452832</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.1003093111524074</v>
+        <v>-6.195184290056474</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6470</v>
+        <v>6417</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>221.0157219985048</v>
+        <v>248.0022481125078</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>41.7</v>
+        <v>106</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>31.47790788198487</v>
+        <v>36.25788448581031</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>45.24200980157727</v>
+        <v>24.44116476204221</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.305747616997572</v>
+        <v>0.4984329999839432</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.1692791265242839</v>
+        <v>0.1360725681308814</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6235</v>
+        <v>6208</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>218.959865629963</v>
+        <v>231.7194974185409</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>39.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>52.33936299904266</v>
+        <v>48.75243337362296</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.43646807099798</v>
+        <v>8.855367057162718</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.130150567078948</v>
+        <v>0.4538354739187082</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1474686836683338</v>
+        <v>0.3786491525577542</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6201</v>
+        <v>6246</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>195.9384742754995</v>
+        <v>230.0189223566711</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>44.7</v>
+        <v>12.55</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>33.20138942294408</v>
+        <v>45.65471023008184</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>25.68379339356792</v>
+        <v>20.53521358791538</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.250045206321652</v>
+        <v>0.3358940919900492</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0279425343533828</v>
+        <v>0.1003093111810259</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6282</v>
+        <v>6470</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>189.2807279905312</v>
+        <v>221.0157219985047</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>45.15</v>
+        <v>41.7</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>43.2783597406161</v>
+        <v>31.47790789153193</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.18843204978721</v>
+        <v>45.24200979585836</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.585128500530534</v>
+        <v>1.305747616997572</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1102064400842133</v>
+        <v>0.1692791263334889</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6272</v>
+        <v>6201</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>175.2513363168909</v>
+        <v>195.9384742754995</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>24.1</v>
+        <v>44.7</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>43.90364422614604</v>
+        <v>33.20138941267766</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>43.09913342562735</v>
+        <v>25.68379357900683</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.6664597938358339</v>
+        <v>0.250045206321652</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.2425426745511598</v>
+        <v>0.0279425343533828</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6276</v>
+        <v>6282</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>168.840492838696</v>
+        <v>189.2807279905312</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>20.2</v>
+        <v>45.15</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>49.48054220529075</v>
+        <v>43.27835976985307</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>23.49337318819044</v>
+        <v>17.18843219106673</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.041598882020045</v>
+        <v>0.585128500530534</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,11 +6453,11 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.2336167454512698</v>
+        <v>0.1102064398647979</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>32.02107746071242</v>
+        <v>32.02107747432268</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.68463805902691</v>
+        <v>13.68463805705331</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.877825846658154</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.09799361129565939</v>
+        <v>-0.097993611381514</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>149.9587408920906</v>
+        <v>149.9587408920903</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>51.5</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>48.84047952142263</v>
+        <v>48.84047930797211</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.23228331515577</v>
+        <v>14.23228342221313</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.864041778058947</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0016088624366497</v>
+        <v>0.0016088624557315</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>46.97933698210426</v>
+        <v>46.97933692667444</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>9.072147998135508</v>
+        <v>9.072148000025308</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.5019934988153797</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0920261622945848</v>
+        <v>0.0920261622182668</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>123.6159576626453</v>
+        <v>123.6159576626449</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>17.3</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>51.33841295316483</v>
+        <v>51.33841295894978</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>6.627924109969396</v>
+        <v>6.627924066839396</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.6877689279501968</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.6265559535630787</v>
+        <v>0.6265559533436655</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>85.61342333645224</v>
+        <v>85.61342333645223</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>59.7</v>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>31.14627398321021</v>
+        <v>31.1462740193267</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>17.3864784231491</v>
+        <v>17.38647842103788</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>1.087682343522149</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.1127536980111381</v>
+        <v>0.1127536976867815</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
